--- a/Output/Tables/baseline_inicial.xlsx
+++ b/Output/Tables/baseline_inicial.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -351,7 +351,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>[ALL]   N=1949</t>
+          <t>[ALL]   N=2225</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -363,233 +363,233 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sex (female), N (%)</t>
+          <t>Sex (female), N (%):</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1396 (71.6%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Age (years), Median [25th;75th]</t>
+          <t xml:space="preserve">    No</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>90.7 [85.8;94.6]</t>
+          <t xml:space="preserve">  558 (25.1%)   </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Years in home-based program, Median [25th;75th]</t>
+          <t xml:space="preserve">    Yes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.12 [1.18;3.96]</t>
+          <t xml:space="preserve">  1374 (61.8%)  </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Distance from center (meters), Median [25th;75th]</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 761 [525;1067] </t>
+          <t xml:space="preserve">  293 (13.2%)   </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Time_walking to center (minutes), Median [25th;75th]</t>
+          <t>Age (years), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.00 [6.00;13.0]</t>
+          <t>90.4 [84.8;94.2]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High comorbidity status (AMG index ≥p85), N (%)</t>
+          <t>Years in home-based program, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1838 (94.3%)  </t>
+          <t>1.89 [0.88;3.76]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>No. registered chronic diseases, Median [25th;75th]</t>
+          <t>High comorbidity status (AMG index ≥p85), N (%)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.0 [8.00;14.0]</t>
+          <t xml:space="preserve">  2083 (93.6%)  </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Commorbidity and complexity, Median [25th;75th]</t>
+          <t>No. registered chronic diseases, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18.6 [13.6;24.5]</t>
+          <t>11.0 [8.00;14.0]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>2220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fragil Vig index, Median [25th;75th]</t>
+          <t>Commorbidity and complexity, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.36 [0.28;0.48]</t>
+          <t>18.5 [13.6;24.5]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">763 </t>
+          <t>2217</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PCC, N (%)</t>
+          <t>Fragil Vig index, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1526 (78.3%)  </t>
+          <t>0.36 [0.28;0.48]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">866 </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MACA, N (%)</t>
+          <t>PCC, N (%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  160 (8.21%)   </t>
+          <t xml:space="preserve">  1664 (74.8%)  </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dependency according to Barthel Index for Activities of Daily Living, N (%):</t>
+          <t>MACA, N (%)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  186 (8.36%)   </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Total (&lt;20)</t>
+          <t>Dependency according to Barthel Index for Activities of Daily Living, N (%):</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  208 (10.7%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Severe (20-35)</t>
+          <t xml:space="preserve">    Total (&lt;20)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  256 (13.1%)   </t>
+          <t xml:space="preserve">  216 (9.71%)   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -601,12 +601,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (40-55)</t>
+          <t xml:space="preserve">    Severe (20-35)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  453 (23.2%)   </t>
+          <t xml:space="preserve">  269 (12.1%)   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -618,12 +618,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Low (60-99)</t>
+          <t xml:space="preserve">    Moderate (40-55)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  991 (50.8%)   </t>
+          <t xml:space="preserve">  495 (22.2%)   </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None (100)</t>
+          <t xml:space="preserve">    Low (60-99)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   33 (1.69%)   </t>
+          <t xml:space="preserve">  1145 (51.5%)  </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -652,12 +652,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    None (100)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (0.41%)    </t>
+          <t xml:space="preserve">   46 (2.07%)   </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -669,46 +669,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Braden, N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">   54 (2.43%)   </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Very high (≤9 to 12)</t>
+          <t>Braden, N (%):</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   88 (4.52%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (13-14)</t>
+          <t xml:space="preserve">    Very high (≤9 to 12)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  192 (9.85%)   </t>
+          <t xml:space="preserve">   93 (4.18%)   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -720,12 +720,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None or Low (15 to 18)</t>
+          <t xml:space="preserve">    Moderate (13-14)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1632 (83.7%)  </t>
+          <t xml:space="preserve">  204 (9.17%)   </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -737,12 +737,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    None or Low (15 to 18)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   37 (1.90%)   </t>
+          <t xml:space="preserve">  1818 (81.7%)  </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -754,46 +754,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Short Portable Mental Status Questionnaire, N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  110 (4.94%)   </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No deficit (0-2 mistakes)</t>
+          <t>Short Portable Mental Status Questionnaire, N (%):</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1060 (54.4%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Low (3-4 mistakes)</t>
+          <t xml:space="preserve">    No deficit (0-2 mistakes)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  288 (14.8%)   </t>
+          <t xml:space="preserve">  1220 (54.8%)  </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -805,12 +805,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (5-7 mistakes)</t>
+          <t xml:space="preserve">    Low (3-4 mistakes)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  266 (13.6%)   </t>
+          <t xml:space="preserve">  315 (14.2%)   </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -822,12 +822,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Severe (8-10 mistakes)</t>
+          <t xml:space="preserve">    Moderate (5-7 mistakes)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  322 (16.5%)   </t>
+          <t xml:space="preserve">  283 (12.7%)   </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Severe (8-10 mistakes)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">   13 (0.67%)   </t>
+          <t xml:space="preserve">  344 (15.5%)   </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -856,46 +856,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Incontinence, N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">   63 (2.83%)   </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fecal and urinary</t>
+          <t>Incontinence, N (%):</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  248 (12.7%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fecal</t>
+          <t xml:space="preserve">    Fecal and urinary</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (0.41%)    </t>
+          <t xml:space="preserve">  241 (10.8%)   </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Urinary</t>
+          <t xml:space="preserve">    Fecal</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1002 (51.4%)  </t>
+          <t xml:space="preserve">   8 (0.36%)    </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None/None registered</t>
+          <t xml:space="preserve">    Urinary</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  691 (35.5%)   </t>
+          <t xml:space="preserve">  975 (43.8%)   </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -941,46 +941,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Social risk, N (%):</t>
+          <t xml:space="preserve">    None/None registered</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1001 (45.0%)  </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No</t>
+          <t>Social risk, N (%):</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1165 (59.8%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Yes</t>
+          <t xml:space="preserve">    No</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  231 (11.9%)   </t>
+          <t xml:space="preserve">  1293 (58.1%)  </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -992,12 +992,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Yes</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  553 (28.4%)   </t>
+          <t xml:space="preserve">  252 (11.3%)   </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1009,46 +1009,46 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Social Risk (TIRS categorized), N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  680 (30.6%)   </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no</t>
+          <t>Social Risk (TIRS categorized), N (%):</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1321 (67.8%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    si</t>
+          <t xml:space="preserve">    no</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  618 (31.7%)   </t>
+          <t xml:space="preserve">  1447 (65.0%)  </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    si</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   10 (0.51%)   </t>
+          <t xml:space="preserve">  706 (31.7%)   </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1077,97 +1077,97 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Social Risk (TIRS numeric), Median [25th;75th]</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0.00 [0.00;1.00]</t>
+          <t xml:space="preserve">   72 (3.24%)   </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Living alone, N (%)</t>
+          <t>Social Risk (TIRS numeric), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  383 (19.7%)   </t>
+          <t>0.00 [0.00;1.00]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2153</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Need for any household adaptation, N (%)</t>
+          <t>Living alone, N (%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  510 (26.2%)   </t>
+          <t xml:space="preserve">  429 (19.3%)   </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Healthcare center, N (%):</t>
+          <t>Need for any household adaptation, N (%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  590 (26.5%)   </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t>Healthcare center, N (%):</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  708 (36.3%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  278 (14.3%)   </t>
+          <t xml:space="preserve">  781 (35.1%)   </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  963 (49.4%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1196,29 +1196,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PHC Home Base organization, N (%):</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1131 (50.8%)  </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  708 (36.3%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1230,29 +1230,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t>PHC Home Base organization, N (%):</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  278 (14.3%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  339 (17.4%)   </t>
+          <t xml:space="preserve">  781 (35.1%)   </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta_reforc</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  624 (32.0%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1281,29 +1281,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>organit_atdom_2, N (%):</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  411 (18.5%)   </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Borrell</t>
+          <t xml:space="preserve">    UAB_consulta_reforc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  394 (20.2%)   </t>
+          <t xml:space="preserve">  720 (32.4%)   </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Casanova</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  278 (14.3%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1332,29 +1332,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_1</t>
+          <t>organit_atdom_2, N (%):</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  183 (9.39%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_2</t>
+          <t xml:space="preserve">    Borrell</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  156 (8.00%)   </t>
+          <t xml:space="preserve">  440 (19.8%)   </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Marc_Aureli</t>
+          <t xml:space="preserve">    Casanova</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  287 (14.7%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1383,12 +1383,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Sant_Elies</t>
+          <t xml:space="preserve">    Montnegre_1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  337 (17.3%)   </t>
+          <t xml:space="preserve">  224 (10.1%)   </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Lluch</t>
+          <t xml:space="preserve">    Montnegre_2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  314 (16.1%)   </t>
+          <t xml:space="preserve">  187 (8.40%)   </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1417,323 +1417,391 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Heart failure, N (%)</t>
+          <t xml:space="preserve">    Marc_Aureli</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  475 (24.4%)   </t>
+          <t xml:space="preserve">  330 (14.8%)   </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ischemic heart disease, N (%)</t>
+          <t xml:space="preserve">    Sant_Elies</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  239 (12.3%)   </t>
+          <t xml:space="preserve">  390 (17.5%)   </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Arrhythmias, N (%)</t>
+          <t xml:space="preserve">    Lluch</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  646 (33.1%)   </t>
+          <t xml:space="preserve">  341 (15.3%)   </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dementia, N (%)</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  413 (21.2%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Parkinson, N (%)</t>
+          <t>Heart failure, N (%)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  164 (8.41%)   </t>
+          <t xml:space="preserve">  462 (20.8%)   </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Stroke, N (%)</t>
+          <t>Ischemic heart disease, N (%)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">  366 (18.8%)   </t>
+          <t xml:space="preserve">  233 (10.5%)   </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Diabetes, N (%)</t>
+          <t>Arrhythmias, N (%)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  468 (24.0%)   </t>
+          <t xml:space="preserve">  625 (28.1%)   </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hyperlipidemia, N (%)</t>
+          <t>Dementia, N (%)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  287 (14.7%)   </t>
+          <t xml:space="preserve">  394 (17.7%)   </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Chronic Kidney Disease, N (%)</t>
+          <t>Parkinson, N (%)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  691 (35.5%)   </t>
+          <t xml:space="preserve">  157 (7.06%)   </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COPD, N (%)</t>
+          <t>Stroke, N (%)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  357 (18.3%)   </t>
+          <t xml:space="preserve">  352 (15.8%)   </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Respiratory failure, N (%)</t>
+          <t>Diabetes, N (%)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">   55 (2.82%)   </t>
+          <t xml:space="preserve">  450 (20.2%)   </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Osteoarthritis, N (%)</t>
+          <t>Hyperlipidemia, N (%)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1095 (56.2%)  </t>
+          <t xml:space="preserve">  271 (12.2%)   </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hip fracture, N (%)</t>
+          <t>Chronic Kidney Disease, N (%)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">   23 (1.18%)   </t>
+          <t xml:space="preserve">  664 (29.8%)   </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Osteoporosis, N (%)</t>
+          <t>COPD, N (%)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">  536 (27.5%)   </t>
+          <t xml:space="preserve">  351 (15.8%)   </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Depression, N (%)</t>
+          <t>Respiratory failure, N (%)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">  578 (29.7%)   </t>
+          <t xml:space="preserve">   54 (2.43%)   </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Anxiety, N (%)</t>
+          <t>Osteoarthritis, N (%)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">  540 (27.7%)   </t>
+          <t xml:space="preserve">  1057 (47.5%)  </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Anemia, N (%)</t>
+          <t>Hip fracture, N (%)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">  230 (11.8%)   </t>
+          <t xml:space="preserve">   21 (0.94%)   </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Urinary tract infection, N (%)</t>
+          <t>Osteoporosis, N (%)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">  448 (23.0%)   </t>
+          <t xml:space="preserve">  517 (23.2%)   </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Depression, N (%)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  555 (24.9%)   </t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Anxiety, N (%)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  523 (23.5%)   </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Anemia, N (%)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  219 (9.84%)   </t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Urinary tract infection, N (%)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  431 (19.4%)   </t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>Glaucoma, N (%)</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  312 (16.0%)   </t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1949</t>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  301 (13.5%)   </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2225</t>
         </is>
       </c>
     </row>

--- a/Output/Tables/baseline_inicial.xlsx
+++ b/Output/Tables/baseline_inicial.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,114 +465,114 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High comorbidity status (AMG index ≥p85), N (%)</t>
+          <t>Distance from center (meters), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2083 (93.6%)  </t>
+          <t xml:space="preserve"> 761 [527;1073] </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>1883</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>No. registered chronic diseases, Median [25th;75th]</t>
+          <t>Time_walking to center (minutes), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11.0 [8.00;14.0]</t>
+          <t>9.00 [6.00;13.0]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>1883</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Commorbidity and complexity, Median [25th;75th]</t>
+          <t>High comorbidity status (AMG index ≥p85), N (%)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18.5 [13.6;24.5]</t>
+          <t xml:space="preserve">  2083 (93.6%)  </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fragil Vig index, Median [25th;75th]</t>
+          <t>No. registered chronic diseases, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.36 [0.28;0.48]</t>
+          <t>11.0 [8.00;14.0]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">866 </t>
+          <t>2220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PCC, N (%)</t>
+          <t>Commorbidity and complexity, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1664 (74.8%)  </t>
+          <t>18.5 [13.6;24.5]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2217</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MACA, N (%)</t>
+          <t>Fragil Vig index, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  186 (8.36%)   </t>
+          <t>0.36 [0.28;0.48]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">866 </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dependency according to Barthel Index for Activities of Daily Living, N (%):</t>
+          <t>PCC, N (%)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1664 (74.8%)  </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -584,46 +584,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Total (&lt;20)</t>
+          <t>MACA, N (%)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  216 (9.71%)   </t>
+          <t xml:space="preserve">  186 (8.36%)   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Severe (20-35)</t>
+          <t>Dependency according to Barthel Index for Activities of Daily Living, N (%):</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  269 (12.1%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (40-55)</t>
+          <t xml:space="preserve">    Total (&lt;20)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  495 (22.2%)   </t>
+          <t xml:space="preserve">  216 (9.71%)   </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Low (60-99)</t>
+          <t xml:space="preserve">    Severe (20-35)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1145 (51.5%)  </t>
+          <t xml:space="preserve">  269 (12.1%)   </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -652,12 +652,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None (100)</t>
+          <t xml:space="preserve">    Moderate (40-55)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   46 (2.07%)   </t>
+          <t xml:space="preserve">  495 (22.2%)   </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -669,12 +669,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Low (60-99)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (2.43%)   </t>
+          <t xml:space="preserve">  1145 (51.5%)  </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -686,29 +686,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Braden, N (%):</t>
+          <t xml:space="preserve">    None (100)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">   46 (2.07%)   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Very high (≤9 to 12)</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   93 (4.18%)   </t>
+          <t xml:space="preserve">   54 (2.43%)   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -720,29 +720,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (13-14)</t>
+          <t>Braden, N (%):</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  204 (9.17%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None or Low (15 to 18)</t>
+          <t xml:space="preserve">    Very high (≤9 to 12)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1818 (81.7%)  </t>
+          <t xml:space="preserve">   93 (4.18%)   </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Moderate (13-14)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  110 (4.94%)   </t>
+          <t xml:space="preserve">  204 (9.17%)   </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -771,29 +771,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Short Portable Mental Status Questionnaire, N (%):</t>
+          <t xml:space="preserve">    None or Low (15 to 18)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1818 (81.7%)  </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No deficit (0-2 mistakes)</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1220 (54.8%)  </t>
+          <t xml:space="preserve">  110 (4.94%)   </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -805,29 +805,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Low (3-4 mistakes)</t>
+          <t>Short Portable Mental Status Questionnaire, N (%):</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  315 (14.2%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (5-7 mistakes)</t>
+          <t xml:space="preserve">    No deficit (0-2 mistakes)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  283 (12.7%)   </t>
+          <t xml:space="preserve">  1220 (54.8%)  </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Severe (8-10 mistakes)</t>
+          <t xml:space="preserve">    Low (3-4 mistakes)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  344 (15.5%)   </t>
+          <t xml:space="preserve">  315 (14.2%)   </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Moderate (5-7 mistakes)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   63 (2.83%)   </t>
+          <t xml:space="preserve">  283 (12.7%)   </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -873,29 +873,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Incontinence, N (%):</t>
+          <t xml:space="preserve">    Severe (8-10 mistakes)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  344 (15.5%)   </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fecal and urinary</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  241 (10.8%)   </t>
+          <t xml:space="preserve">   63 (2.83%)   </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -907,29 +907,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fecal</t>
+          <t>Incontinence, N (%):</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (0.36%)    </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Urinary</t>
+          <t xml:space="preserve">    Fecal and urinary</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  975 (43.8%)   </t>
+          <t xml:space="preserve">  241 (10.8%)   </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -941,12 +941,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None/None registered</t>
+          <t xml:space="preserve">    Fecal</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1001 (45.0%)  </t>
+          <t xml:space="preserve">   8 (0.36%)    </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -958,29 +958,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Social risk, N (%):</t>
+          <t xml:space="preserve">    Urinary</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  975 (43.8%)   </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No</t>
+          <t xml:space="preserve">    None/None registered</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1293 (58.1%)  </t>
+          <t xml:space="preserve">  1001 (45.0%)  </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -992,29 +992,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Yes</t>
+          <t>Social risk, N (%):</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  252 (11.3%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    No</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  680 (30.6%)   </t>
+          <t xml:space="preserve">  1293 (58.1%)  </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1026,29 +1026,29 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Social Risk (TIRS categorized), N (%):</t>
+          <t xml:space="preserve">    Yes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  252 (11.3%)   </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1447 (65.0%)  </t>
+          <t xml:space="preserve">  680 (30.6%)   </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1060,29 +1060,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    si</t>
+          <t>Social Risk (TIRS categorized), N (%):</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  706 (31.7%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    no</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">   72 (3.24%)   </t>
+          <t xml:space="preserve">  1447 (65.0%)  </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1094,63 +1094,63 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Social Risk (TIRS numeric), Median [25th;75th]</t>
+          <t xml:space="preserve">    si</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.00 [0.00;1.00]</t>
+          <t xml:space="preserve">  706 (31.7%)   </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Living alone, N (%)</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  429 (19.3%)   </t>
+          <t xml:space="preserve">   72 (3.24%)   </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Need for any household adaptation, N (%)</t>
+          <t>Social Risk (TIRS numeric), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  590 (26.5%)   </t>
+          <t>0.00 [0.00;1.00]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2153</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Healthcare center, N (%):</t>
+          <t>Living alone, N (%)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  429 (19.3%)   </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1162,46 +1162,46 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t>Need for any household adaptation, N (%)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  781 (35.1%)   </t>
+          <t xml:space="preserve">  590 (26.5%)   </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t>Healthcare center, N (%):</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1131 (50.8%)  </t>
+          <t xml:space="preserve">  781 (35.1%)   </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1213,12 +1213,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1230,29 +1230,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PHC Home Base organization, N (%):</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1131 (50.8%)  </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  781 (35.1%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1264,29 +1264,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t>PHC Home Base organization, N (%):</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  411 (18.5%)   </t>
+          <t xml:space="preserve">  781 (35.1%)   </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1298,12 +1298,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta_reforc</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  720 (32.4%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">  411 (18.5%)   </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1332,29 +1332,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>organit_atdom_2, N (%):</t>
+          <t xml:space="preserve">    UAB_consulta_reforc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  720 (32.4%)   </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Borrell</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  440 (19.8%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1366,29 +1366,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Casanova</t>
+          <t>organit_atdom_2, N (%):</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_1</t>
+          <t xml:space="preserve">    Borrell</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  224 (10.1%)   </t>
+          <t xml:space="preserve">  440 (19.8%)   </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_2</t>
+          <t xml:space="preserve">    Casanova</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  187 (8.40%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Marc_Aureli</t>
+          <t xml:space="preserve">    Montnegre_1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  330 (14.8%)   </t>
+          <t xml:space="preserve">  224 (10.1%)   </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1434,12 +1434,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Sant_Elies</t>
+          <t xml:space="preserve">    Montnegre_2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  390 (17.5%)   </t>
+          <t xml:space="preserve">  187 (8.40%)   </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Lluch</t>
+          <t xml:space="preserve">    Marc_Aureli</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  341 (15.3%)   </t>
+          <t xml:space="preserve">  330 (14.8%)   </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Sant_Elies</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">  390 (17.5%)   </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1485,46 +1485,46 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Heart failure, N (%)</t>
+          <t xml:space="preserve">    Lluch</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  462 (20.8%)   </t>
+          <t xml:space="preserve">  341 (15.3%)   </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ischemic heart disease, N (%)</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">  233 (10.5%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Arrhythmias, N (%)</t>
+          <t>Heart failure, N (%)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  625 (28.1%)   </t>
+          <t xml:space="preserve">  462 (20.8%)   </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1536,12 +1536,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dementia, N (%)</t>
+          <t>Ischemic heart disease, N (%)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  394 (17.7%)   </t>
+          <t xml:space="preserve">  233 (10.5%)   </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Parkinson, N (%)</t>
+          <t>Arrhythmias, N (%)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  157 (7.06%)   </t>
+          <t xml:space="preserve">  625 (28.1%)   </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Stroke, N (%)</t>
+          <t>Dementia, N (%)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  352 (15.8%)   </t>
+          <t xml:space="preserve">  394 (17.7%)   </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Diabetes, N (%)</t>
+          <t>Parkinson, N (%)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  450 (20.2%)   </t>
+          <t xml:space="preserve">  157 (7.06%)   </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1604,12 +1604,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Hyperlipidemia, N (%)</t>
+          <t>Stroke, N (%)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  271 (12.2%)   </t>
+          <t xml:space="preserve">  352 (15.8%)   </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Chronic Kidney Disease, N (%)</t>
+          <t>Diabetes, N (%)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">  664 (29.8%)   </t>
+          <t xml:space="preserve">  450 (20.2%)   </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COPD, N (%)</t>
+          <t>Hyperlipidemia, N (%)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">  351 (15.8%)   </t>
+          <t xml:space="preserve">  271 (12.2%)   </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Respiratory failure, N (%)</t>
+          <t>Chronic Kidney Disease, N (%)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (2.43%)   </t>
+          <t xml:space="preserve">  664 (29.8%)   </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1672,12 +1672,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Osteoarthritis, N (%)</t>
+          <t>COPD, N (%)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1057 (47.5%)  </t>
+          <t xml:space="preserve">  351 (15.8%)   </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1689,12 +1689,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Hip fracture, N (%)</t>
+          <t>Respiratory failure, N (%)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">   21 (0.94%)   </t>
+          <t xml:space="preserve">   54 (2.43%)   </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1706,12 +1706,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Osteoporosis, N (%)</t>
+          <t>Osteoarthritis, N (%)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">  517 (23.2%)   </t>
+          <t xml:space="preserve">  1057 (47.5%)  </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Depression, N (%)</t>
+          <t>Hip fracture, N (%)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">  555 (24.9%)   </t>
+          <t xml:space="preserve">   21 (0.94%)   </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1740,12 +1740,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Anxiety, N (%)</t>
+          <t>Osteoporosis, N (%)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">  523 (23.5%)   </t>
+          <t xml:space="preserve">  517 (23.2%)   </t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1757,12 +1757,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Anemia, N (%)</t>
+          <t>Depression, N (%)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">  219 (9.84%)   </t>
+          <t xml:space="preserve">  555 (24.9%)   </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Urinary tract infection, N (%)</t>
+          <t>Anxiety, N (%)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">  431 (19.4%)   </t>
+          <t xml:space="preserve">  523 (23.5%)   </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1791,15 +1791,49 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>Anemia, N (%)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  219 (9.84%)   </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Urinary tract infection, N (%)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  431 (19.4%)   </t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>Glaucoma, N (%)</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t xml:space="preserve">  301 (13.5%)   </t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>2225</t>
         </is>

--- a/Output/Tables/baseline_inicial.xlsx
+++ b/Output/Tables/baseline_inicial.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -363,12 +363,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sex (female), N (%):</t>
+          <t>Sex (female), N (%)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1554 (69.8%)  </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -380,63 +380,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No</t>
+          <t>Age (years), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  558 (25.1%)   </t>
+          <t>90.4 [84.8;94.2]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Yes</t>
+          <t>Years in home-based program, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1374 (61.8%)  </t>
+          <t>1.89 [0.88;3.76]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t>Distance from center (meters), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  293 (13.2%)   </t>
+          <t xml:space="preserve"> 765 [527;1070] </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Age (years), Median [25th;75th]</t>
+          <t>Time_walking to center (minutes), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90.4 [84.8;94.2]</t>
+          <t>9.00 [6.00;13.0]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -448,182 +448,182 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Years in home-based program, Median [25th;75th]</t>
+          <t>High comorbidity status (AMG index ≥p85), N (%)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.89 [0.88;3.76]</t>
+          <t xml:space="preserve">  2083 (93.6%)  </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Distance from center (meters), Median [25th;75th]</t>
+          <t>No. registered chronic diseases, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 761 [527;1073] </t>
+          <t>11.0 [8.00;14.0]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>2220</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Time_walking to center (minutes), Median [25th;75th]</t>
+          <t>Commorbidity and complexity, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9.00 [6.00;13.0]</t>
+          <t>18.5 [13.6;24.5]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>2217</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High comorbidity status (AMG index ≥p85), N (%)</t>
+          <t>Fragil Vig index, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2083 (93.6%)  </t>
+          <t>0.36 [0.28;0.48]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">866 </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>No. registered chronic diseases, Median [25th;75th]</t>
+          <t>PCC, N (%)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11.0 [8.00;14.0]</t>
+          <t xml:space="preserve">  1664 (74.8%)  </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Commorbidity and complexity, Median [25th;75th]</t>
+          <t>MACA, N (%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18.5 [13.6;24.5]</t>
+          <t xml:space="preserve">  186 (8.36%)   </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fragil Vig index, Median [25th;75th]</t>
+          <t>Dependency according to Barthel Index for Activities of Daily Living, N (%):</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.36 [0.28;0.48]</t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">866 </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PCC, N (%)</t>
+          <t xml:space="preserve">    Total (&lt;20)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1664 (74.8%)  </t>
+          <t xml:space="preserve">  216 (9.71%)   </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MACA, N (%)</t>
+          <t xml:space="preserve">    Severe (20-35)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  186 (8.36%)   </t>
+          <t xml:space="preserve">  269 (12.1%)   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dependency according to Barthel Index for Activities of Daily Living, N (%):</t>
+          <t xml:space="preserve">    Moderate (40-55)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  495 (22.2%)   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Total (&lt;20)</t>
+          <t xml:space="preserve">    Low (60-99)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  216 (9.71%)   </t>
+          <t xml:space="preserve">  1145 (51.5%)  </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Severe (20-35)</t>
+          <t xml:space="preserve">    None (100)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  269 (12.1%)   </t>
+          <t xml:space="preserve">   46 (2.07%)   </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -652,12 +652,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (40-55)</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  495 (22.2%)   </t>
+          <t xml:space="preserve">   54 (2.43%)   </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -669,29 +669,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Low (60-99)</t>
+          <t>Braden, N (%):</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1145 (51.5%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None (100)</t>
+          <t xml:space="preserve">    Very high (≤9 to 12)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   46 (2.07%)   </t>
+          <t xml:space="preserve">   93 (4.18%)   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Moderate (13-14)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (2.43%)   </t>
+          <t xml:space="preserve">  204 (9.17%)   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -720,29 +720,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Braden, N (%):</t>
+          <t xml:space="preserve">    None or Low (15 to 18)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1818 (81.7%)  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Very high (≤9 to 12)</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   93 (4.18%)   </t>
+          <t xml:space="preserve">  110 (4.94%)   </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -754,29 +754,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (13-14)</t>
+          <t>Short Portable Mental Status Questionnaire, N (%):</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  204 (9.17%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None or Low (15 to 18)</t>
+          <t xml:space="preserve">    No deficit (0-2 mistakes)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1818 (81.7%)  </t>
+          <t xml:space="preserve">  1220 (54.8%)  </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -788,12 +788,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Low (3-4 mistakes)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  110 (4.94%)   </t>
+          <t xml:space="preserve">  315 (14.2%)   </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -805,29 +805,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Short Portable Mental Status Questionnaire, N (%):</t>
+          <t xml:space="preserve">    Moderate (5-7 mistakes)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  283 (12.7%)   </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No deficit (0-2 mistakes)</t>
+          <t xml:space="preserve">    Severe (8-10 mistakes)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1220 (54.8%)  </t>
+          <t xml:space="preserve">  344 (15.5%)   </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Low (3-4 mistakes)</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  315 (14.2%)   </t>
+          <t xml:space="preserve">   63 (2.83%)   </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -856,29 +856,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (5-7 mistakes)</t>
+          <t>Incontinence, N (%):</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  283 (12.7%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Severe (8-10 mistakes)</t>
+          <t xml:space="preserve">    Fecal and urinary</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  344 (15.5%)   </t>
+          <t xml:space="preserve">  241 (10.8%)   </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Fecal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   63 (2.83%)   </t>
+          <t xml:space="preserve">   8 (0.36%)    </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -907,29 +907,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Incontinence, N (%):</t>
+          <t xml:space="preserve">    Urinary</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  975 (43.8%)   </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fecal and urinary</t>
+          <t xml:space="preserve">    None/None registered</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  241 (10.8%)   </t>
+          <t xml:space="preserve">  1001 (45.0%)  </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -941,29 +941,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fecal</t>
+          <t>Social risk, N (%):</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (0.36%)    </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Urinary</t>
+          <t xml:space="preserve">    No</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  975 (43.8%)   </t>
+          <t xml:space="preserve">  1293 (58.1%)  </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -975,12 +975,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None/None registered</t>
+          <t xml:space="preserve">    Yes</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1001 (45.0%)  </t>
+          <t xml:space="preserve">  252 (11.3%)   </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -992,46 +992,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Social risk, N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  680 (30.6%)   </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No</t>
+          <t>Social Risk (TIRS categorized), N (%):</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1293 (58.1%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Yes</t>
+          <t xml:space="preserve">    no</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  252 (11.3%)   </t>
+          <t xml:space="preserve">  1447 (65.0%)  </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1043,12 +1043,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    si</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  680 (30.6%)   </t>
+          <t xml:space="preserve">  706 (31.7%)   </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1060,148 +1060,148 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Social Risk (TIRS categorized), N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">   72 (3.24%)   </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no</t>
+          <t>Social Risk (TIRS numeric), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1447 (65.0%)  </t>
+          <t>0.00 [0.00;1.00]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2153</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    si</t>
+          <t>Living alone, N (%)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  706 (31.7%)   </t>
+          <t xml:space="preserve">  429 (19.3%)   </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t>Need for any household adaptation, N (%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">   72 (3.24%)   </t>
+          <t xml:space="preserve">  590 (26.5%)   </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Social Risk (TIRS numeric), Median [25th;75th]</t>
+          <t>Healthcare center, N (%):</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.00 [0.00;1.00]</t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Living alone, N (%)</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  429 (19.3%)   </t>
+          <t xml:space="preserve">  781 (35.1%)   </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Need for any household adaptation, N (%)</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  590 (26.5%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Healthcare center, N (%):</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1131 (50.8%)  </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  781 (35.1%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1213,29 +1213,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t>PHC Home Base organization, N (%):</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1131 (50.8%)  </t>
+          <t xml:space="preserve">  781 (35.1%)   </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1247,12 +1247,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1264,29 +1264,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PHC Home Base organization, N (%):</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  411 (18.5%)   </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t xml:space="preserve">    UAB_consulta_reforc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  781 (35.1%)   </t>
+          <t xml:space="preserve">  720 (32.4%)   </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1298,12 +1298,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1315,29 +1315,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t>organit_atdom_2, N (%):</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  411 (18.5%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta_reforc</t>
+          <t xml:space="preserve">    Borrell</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  720 (32.4%)   </t>
+          <t xml:space="preserve">  440 (19.8%)   </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Casanova</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1366,29 +1366,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>organit_atdom_2, N (%):</t>
+          <t xml:space="preserve">    Montnegre_1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  224 (10.1%)   </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Borrell</t>
+          <t xml:space="preserve">    Montnegre_2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  440 (19.8%)   </t>
+          <t xml:space="preserve">  187 (8.40%)   </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Casanova</t>
+          <t xml:space="preserve">    Marc_Aureli</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">  330 (14.8%)   </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_1</t>
+          <t xml:space="preserve">    Sant_Elies</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  224 (10.1%)   </t>
+          <t xml:space="preserve">  390 (17.5%)   </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1434,12 +1434,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_2</t>
+          <t xml:space="preserve">    Lluch</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  187 (8.40%)   </t>
+          <t xml:space="preserve">  341 (15.3%)   </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Marc_Aureli</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  330 (14.8%)   </t>
+          <t xml:space="preserve">   1 (0.04%)    </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1468,63 +1468,63 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Sant_Elies</t>
+          <t>Heart failure, N (%)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  390 (17.5%)   </t>
+          <t xml:space="preserve">  462 (20.8%)   </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Lluch</t>
+          <t>Ischemic heart disease, N (%)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  341 (15.3%)   </t>
+          <t xml:space="preserve">  233 (10.5%)   </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t>Arrhythmias, N (%)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">  625 (28.1%)   </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2225</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Heart failure, N (%)</t>
+          <t>Dementia, N (%)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  462 (20.8%)   </t>
+          <t xml:space="preserve">  394 (17.7%)   </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1536,12 +1536,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ischemic heart disease, N (%)</t>
+          <t>Parkinson, N (%)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  233 (10.5%)   </t>
+          <t xml:space="preserve">  157 (7.06%)   </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Arrhythmias, N (%)</t>
+          <t>Stroke, N (%)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  625 (28.1%)   </t>
+          <t xml:space="preserve">  352 (15.8%)   </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dementia, N (%)</t>
+          <t>Diabetes, N (%)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  394 (17.7%)   </t>
+          <t xml:space="preserve">  450 (20.2%)   </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Parkinson, N (%)</t>
+          <t>Hyperlipidemia, N (%)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  157 (7.06%)   </t>
+          <t xml:space="preserve">  271 (12.2%)   </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1604,12 +1604,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Stroke, N (%)</t>
+          <t>Chronic Kidney Disease, N (%)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  352 (15.8%)   </t>
+          <t xml:space="preserve">  664 (29.8%)   </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Diabetes, N (%)</t>
+          <t>COPD, N (%)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">  450 (20.2%)   </t>
+          <t xml:space="preserve">  351 (15.8%)   </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Hyperlipidemia, N (%)</t>
+          <t>Respiratory failure, N (%)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">  271 (12.2%)   </t>
+          <t xml:space="preserve">   54 (2.43%)   </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Chronic Kidney Disease, N (%)</t>
+          <t>Osteoarthritis, N (%)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">  664 (29.8%)   </t>
+          <t xml:space="preserve">  1057 (47.5%)  </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1672,12 +1672,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>COPD, N (%)</t>
+          <t>Hip fracture, N (%)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">  351 (15.8%)   </t>
+          <t xml:space="preserve">   21 (0.94%)   </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1689,12 +1689,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Respiratory failure, N (%)</t>
+          <t>Osteoporosis, N (%)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (2.43%)   </t>
+          <t xml:space="preserve">  517 (23.2%)   </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1706,12 +1706,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Osteoarthritis, N (%)</t>
+          <t>Depression, N (%)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1057 (47.5%)  </t>
+          <t xml:space="preserve">  555 (24.9%)   </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hip fracture, N (%)</t>
+          <t>Anxiety, N (%)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">   21 (0.94%)   </t>
+          <t xml:space="preserve">  523 (23.5%)   </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1740,12 +1740,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Osteoporosis, N (%)</t>
+          <t>Anemia, N (%)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">  517 (23.2%)   </t>
+          <t xml:space="preserve">  219 (9.84%)   </t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1757,12 +1757,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Depression, N (%)</t>
+          <t>Urinary tract infection, N (%)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">  555 (24.9%)   </t>
+          <t xml:space="preserve">  431 (19.4%)   </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1774,66 +1774,15 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Anxiety, N (%)</t>
+          <t>Glaucoma, N (%)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">  523 (23.5%)   </t>
+          <t xml:space="preserve">  301 (13.5%)   </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
-        <is>
-          <t>2225</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Anemia, N (%)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  219 (9.84%)   </t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2225</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Urinary tract infection, N (%)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  431 (19.4%)   </t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2225</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Glaucoma, N (%)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  301 (13.5%)   </t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
         <is>
           <t>2225</t>
         </is>

--- a/Output/Tables/baseline_inicial.xlsx
+++ b/Output/Tables/baseline_inicial.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -351,7 +351,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>[ALL]   N=2225</t>
+          <t>[ALL]   N=2221</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -368,12 +368,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1554 (69.8%)  </t>
+          <t xml:space="preserve">  1551 (69.8%)  </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -390,7 +390,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -424,7 +424,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -441,7 +441,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -453,12 +453,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2083 (93.6%)  </t>
+          <t xml:space="preserve">  2080 (93.7%)  </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2217</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18.5 [13.6;24.5]</t>
+          <t>18.5 [13.6;24.4]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2214</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1664 (74.8%)  </t>
+          <t xml:space="preserve">  1662 (74.8%)  </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  186 (8.36%)   </t>
+          <t xml:space="preserve">  186 (8.37%)   </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  216 (9.71%)   </t>
+          <t xml:space="preserve">  216 (9.73%)   </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  495 (22.2%)   </t>
+          <t xml:space="preserve">  495 (22.3%)   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1145 (51.5%)  </t>
+          <t xml:space="preserve">  1145 (51.6%)  </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (2.43%)   </t>
+          <t xml:space="preserve">   50 (2.25%)   </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   93 (4.18%)   </t>
+          <t xml:space="preserve">   93 (4.19%)   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  204 (9.17%)   </t>
+          <t xml:space="preserve">  204 (9.19%)   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1818 (81.7%)  </t>
+          <t xml:space="preserve">  1818 (81.9%)  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  110 (4.94%)   </t>
+          <t xml:space="preserve">  106 (4.77%)   </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1220 (54.8%)  </t>
+          <t xml:space="preserve">  1219 (54.9%)  </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">   63 (2.83%)   </t>
+          <t xml:space="preserve">   60 (2.70%)   </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  241 (10.8%)   </t>
+          <t xml:space="preserve">  241 (10.9%)   </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  975 (43.8%)   </t>
+          <t xml:space="preserve">  975 (43.9%)   </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1001 (45.0%)  </t>
+          <t xml:space="preserve">  997 (44.9%)   </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1293 (58.1%)  </t>
+          <t xml:space="preserve">  1293 (58.2%)  </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  680 (30.6%)   </t>
+          <t xml:space="preserve">  676 (30.4%)   </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1447 (65.0%)  </t>
+          <t xml:space="preserve">  1447 (65.2%)  </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  706 (31.7%)   </t>
+          <t xml:space="preserve">  706 (31.8%)   </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   72 (3.24%)   </t>
+          <t xml:space="preserve">   68 (3.06%)   </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  429 (19.3%)   </t>
+          <t xml:space="preserve">  428 (19.3%)   </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  590 (26.5%)   </t>
+          <t xml:space="preserve">  590 (26.6%)   </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  781 (35.1%)   </t>
+          <t xml:space="preserve">  780 (35.1%)   </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1131 (50.8%)  </t>
+          <t xml:space="preserve">  1129 (50.8%)  </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1196,46 +1196,46 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t>PHC Home Base organization, N (%):</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PHC Home Base organization, N (%):</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  780 (35.1%)   </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  781 (35.1%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1247,12 +1247,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">  410 (18.5%)   </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t xml:space="preserve">    UAB_consulta_reforc</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  411 (18.5%)   </t>
+          <t xml:space="preserve">  719 (32.4%)   </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1281,29 +1281,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta_reforc</t>
+          <t>organit_atdom_2, N (%):</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  720 (32.4%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Borrell</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">  440 (19.8%)   </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1315,29 +1315,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>organit_atdom_2, N (%):</t>
+          <t xml:space="preserve">    Casanova</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Borrell</t>
+          <t xml:space="preserve">    Montnegre_1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  440 (19.8%)   </t>
+          <t xml:space="preserve">  223 (10.0%)   </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Casanova</t>
+          <t xml:space="preserve">    Montnegre_2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">  187 (8.42%)   </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_1</t>
+          <t xml:space="preserve">    Marc_Aureli</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  224 (10.1%)   </t>
+          <t xml:space="preserve">  331 (14.9%)   </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1383,12 +1383,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_2</t>
+          <t xml:space="preserve">    Sant_Elies</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  187 (8.40%)   </t>
+          <t xml:space="preserve">  388 (17.5%)   </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Marc_Aureli</t>
+          <t xml:space="preserve">    Lluch</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  330 (14.8%)   </t>
+          <t xml:space="preserve">  340 (15.3%)   </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1417,374 +1417,391 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Sant_Elies</t>
+          <t>Heart failure, N (%)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  390 (17.5%)   </t>
+          <t xml:space="preserve">  462 (20.8%)   </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Lluch</t>
+          <t>Ischemic heart disease, N (%)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  341 (15.3%)   </t>
+          <t xml:space="preserve">  233 (10.5%)   </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t>Arrhythmias, N (%)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.04%)    </t>
+          <t xml:space="preserve">  625 (28.1%)   </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Heart failure, N (%)</t>
+          <t>Dementia, N (%)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  462 (20.8%)   </t>
+          <t xml:space="preserve">  394 (17.7%)   </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ischemic heart disease, N (%)</t>
+          <t>Parkinson, N (%)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  233 (10.5%)   </t>
+          <t xml:space="preserve">  157 (7.07%)   </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Arrhythmias, N (%)</t>
+          <t>Stroke, N (%)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">  625 (28.1%)   </t>
+          <t xml:space="preserve">  352 (15.8%)   </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dementia, N (%)</t>
+          <t>Diabetes, N (%)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  394 (17.7%)   </t>
+          <t xml:space="preserve">  450 (20.3%)   </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Parkinson, N (%)</t>
+          <t>Hyperlipidemia, N (%)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  157 (7.06%)   </t>
+          <t xml:space="preserve">  271 (12.2%)   </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Stroke, N (%)</t>
+          <t>Chronic Kidney Disease, N (%)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  352 (15.8%)   </t>
+          <t xml:space="preserve">  664 (29.9%)   </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Diabetes, N (%)</t>
+          <t>COPD, N (%)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  450 (20.2%)   </t>
+          <t xml:space="preserve">  351 (15.8%)   </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Hyperlipidemia, N (%)</t>
+          <t>Respiratory failure, N (%)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  271 (12.2%)   </t>
+          <t xml:space="preserve">   54 (2.43%)   </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Chronic Kidney Disease, N (%)</t>
+          <t>Osteoarthritis, N (%)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  664 (29.8%)   </t>
+          <t xml:space="preserve">  1057 (47.6%)  </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COPD, N (%)</t>
+          <t>Hip fracture, N (%)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">  351 (15.8%)   </t>
+          <t xml:space="preserve">   21 (0.95%)   </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Respiratory failure, N (%)</t>
+          <t>Osteoporosis, N (%)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (2.43%)   </t>
+          <t xml:space="preserve">  517 (23.3%)   </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Osteoarthritis, N (%)</t>
+          <t>Depression, N (%)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1057 (47.5%)  </t>
+          <t xml:space="preserve">  555 (25.0%)   </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Hip fracture, N (%)</t>
+          <t>Anxiety, N (%)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">   21 (0.94%)   </t>
+          <t xml:space="preserve">  523 (23.5%)   </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Osteoporosis, N (%)</t>
+          <t>Anemia, N (%)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">  517 (23.2%)   </t>
+          <t xml:space="preserve">  219 (9.86%)   </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Depression, N (%)</t>
+          <t>Urinary tract infection, N (%)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">  555 (24.9%)   </t>
+          <t xml:space="preserve">  431 (19.4%)   </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Anxiety, N (%)</t>
+          <t>Glaucoma, N (%)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">  523 (23.5%)   </t>
+          <t xml:space="preserve">  301 (13.6%)   </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Anemia, N (%)</t>
+          <t>Chronic_heart_failure, N (%)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">  219 (9.84%)   </t>
+          <t xml:space="preserve">  462 (20.8%)   </t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Urinary tract infection, N (%)</t>
+          <t>Cancer, N (%)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">  431 (19.4%)   </t>
+          <t xml:space="preserve">   79 (3.56%)   </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Glaucoma, N (%)</t>
+          <t>Metástasis, N (%)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">  301 (13.5%)   </t>
+          <t xml:space="preserve">   25 (1.13%)   </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2221</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Liver_disease, N (%)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   9 (0.41%)    </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2221</t>
         </is>
       </c>
     </row>

--- a/Output/Tables/baseline_inicial.xlsx
+++ b/Output/Tables/baseline_inicial.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -402,7 +402,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.89 [0.88;3.76]</t>
+          <t>1.92 [0.92;3.79]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -465,80 +465,80 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>No. registered chronic diseases, Median [25th;75th]</t>
+          <t>GMA Groups, Incidence at time=.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.0 [8.00;14.0]</t>
+          <t xml:space="preserve">       .        </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t xml:space="preserve"> 0  </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Commorbidity and complexity, Median [25th;75th]</t>
+          <t>No. registered chronic diseases, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18.5 [13.6;24.4]</t>
+          <t>11.0 [8.00;14.0]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2217</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fragil Vig index, Median [25th;75th]</t>
+          <t>Commorbidity and complexity, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.36 [0.28;0.48]</t>
+          <t>18.5 [13.6;24.4]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">866 </t>
+          <t>2214</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PCC, N (%)</t>
+          <t>Fragil Vig index, Median [25th;75th]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1662 (74.8%)  </t>
+          <t>0.36 [0.28;0.48]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">866 </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MACA, N (%)</t>
+          <t>PCC, N (%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  186 (8.37%)   </t>
+          <t xml:space="preserve">  1662 (74.8%)  </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dependency according to Barthel Index for Activities of Daily Living, N (%):</t>
+          <t>MACA, N (%)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  186 (8.37%)   </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -567,29 +567,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Total (&lt;20)</t>
+          <t>Dependency according to Barthel Index for Activities of Daily Living, N (%):</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  216 (9.73%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Severe (20-35)</t>
+          <t xml:space="preserve">    Total (&lt;20)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  269 (12.1%)   </t>
+          <t xml:space="preserve">  216 (9.73%)   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -601,12 +601,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (40-55)</t>
+          <t xml:space="preserve">    Severe (20-35)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  495 (22.3%)   </t>
+          <t xml:space="preserve">  269 (12.1%)   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -618,12 +618,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Low (60-99)</t>
+          <t xml:space="preserve">    Moderate (40-55)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1145 (51.6%)  </t>
+          <t xml:space="preserve">  495 (22.3%)   </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None (100)</t>
+          <t xml:space="preserve">    Low (60-99)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   46 (2.07%)   </t>
+          <t xml:space="preserve">  1145 (51.6%)  </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -652,12 +652,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    None (100)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   50 (2.25%)   </t>
+          <t xml:space="preserve">   46 (2.07%)   </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -669,46 +669,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Braden, N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">   50 (2.25%)   </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Very high (≤9 to 12)</t>
+          <t>Braden, N (%):</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   93 (4.19%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (13-14)</t>
+          <t xml:space="preserve">    Very high (≤9 to 12)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  204 (9.19%)   </t>
+          <t xml:space="preserve">   93 (4.19%)   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -720,12 +720,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None or Low (15 to 18)</t>
+          <t xml:space="preserve">    Moderate (13-14)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1818 (81.9%)  </t>
+          <t xml:space="preserve">  204 (9.19%)   </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -737,12 +737,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    None or Low (15 to 18)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  106 (4.77%)   </t>
+          <t xml:space="preserve">  1818 (81.9%)  </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -754,46 +754,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Short Portable Mental Status Questionnaire, N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  106 (4.77%)   </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No deficit (0-2 mistakes)</t>
+          <t>Short Portable Mental Status Questionnaire, N (%):</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1219 (54.9%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Low (3-4 mistakes)</t>
+          <t xml:space="preserve">    No deficit (0-2 mistakes)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  315 (14.2%)   </t>
+          <t xml:space="preserve">  1219 (54.9%)  </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -805,12 +805,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Moderate (5-7 mistakes)</t>
+          <t xml:space="preserve">    Low (3-4 mistakes)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  283 (12.7%)   </t>
+          <t xml:space="preserve">  315 (14.2%)   </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -822,12 +822,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Severe (8-10 mistakes)</t>
+          <t xml:space="preserve">    Moderate (5-7 mistakes)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  344 (15.5%)   </t>
+          <t xml:space="preserve">  283 (12.7%)   </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Severe (8-10 mistakes)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">   60 (2.70%)   </t>
+          <t xml:space="preserve">  344 (15.5%)   </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -856,46 +856,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Incontinence, N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">   60 (2.70%)   </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fecal and urinary</t>
+          <t>Incontinence, N (%):</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  241 (10.9%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Fecal</t>
+          <t xml:space="preserve">    Fecal and urinary</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (0.36%)    </t>
+          <t xml:space="preserve">  241 (10.9%)   </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Urinary</t>
+          <t xml:space="preserve">    Fecal</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  975 (43.9%)   </t>
+          <t xml:space="preserve">   8 (0.36%)    </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    None/None registered</t>
+          <t xml:space="preserve">    Urinary</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  997 (44.9%)   </t>
+          <t xml:space="preserve">  975 (43.9%)   </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -941,46 +941,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Social risk, N (%):</t>
+          <t xml:space="preserve">    None/None registered</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  997 (44.9%)   </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    No</t>
+          <t>Social risk, N (%):</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1293 (58.2%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Yes</t>
+          <t xml:space="preserve">    No</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  252 (11.3%)   </t>
+          <t xml:space="preserve">  1293 (58.2%)  </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -992,12 +992,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    Yes</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  676 (30.4%)   </t>
+          <t xml:space="preserve">  252 (11.3%)   </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1009,46 +1009,46 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Social Risk (TIRS categorized), N (%):</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  676 (30.4%)   </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no</t>
+          <t>Social Risk (TIRS categorized), N (%):</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1447 (65.2%)  </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    si</t>
+          <t xml:space="preserve">    no</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  706 (31.8%)   </t>
+          <t xml:space="preserve">  1447 (65.2%)  </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Missing'</t>
+          <t xml:space="preserve">    si</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   68 (3.06%)   </t>
+          <t xml:space="preserve">  706 (31.8%)   </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1077,46 +1077,46 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Social Risk (TIRS numeric), Median [25th;75th]</t>
+          <t xml:space="preserve">    'Missing'</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0.00 [0.00;1.00]</t>
+          <t xml:space="preserve">   68 (3.06%)   </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Living alone, N (%)</t>
+          <t>Social Risk (TIRS numeric), Median [25th;75th]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  428 (19.3%)   </t>
+          <t>0.00 [0.00;1.00]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2153</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Need for any household adaptation, N (%)</t>
+          <t>Living alone, N (%)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  590 (26.6%)   </t>
+          <t xml:space="preserve">  428 (19.3%)   </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1128,12 +1128,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Healthcare center, N (%):</t>
+          <t>Need for any household adaptation, N (%)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  590 (26.6%)   </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1145,29 +1145,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t>Healthcare center, N (%):</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  780 (35.1%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">  780 (35.1%)   </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1129 (50.8%)  </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1196,46 +1196,46 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PHC Home Base organization, N (%):</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  1129 (50.8%)  </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Atdom</t>
+          <t>PHC Home Base organization, N (%):</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  780 (35.1%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equip_Inf</t>
+          <t xml:space="preserve">    Equip_Atdom</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">  780 (35.1%)   </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1247,12 +1247,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta</t>
+          <t xml:space="preserve">    Equip_Inf</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  410 (18.5%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UAB_consulta_reforc</t>
+          <t xml:space="preserve">    UAB_consulta</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  719 (32.4%)   </t>
+          <t xml:space="preserve">  410 (18.5%)   </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1281,46 +1281,46 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>organit_atdom_2, N (%):</t>
+          <t xml:space="preserve">    UAB_consulta_reforc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">                </t>
+          <t xml:space="preserve">  719 (32.4%)   </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Borrell</t>
+          <t>organit_atdom_2, N (%):</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  440 (19.8%)   </t>
+          <t xml:space="preserve">                </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t>2221</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Casanova</t>
+          <t xml:space="preserve">    Borrell</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  312 (14.0%)   </t>
+          <t xml:space="preserve">  440 (19.8%)   </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1332,12 +1332,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_1</t>
+          <t xml:space="preserve">    Casanova</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  223 (10.0%)   </t>
+          <t xml:space="preserve">  312 (14.0%)   </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Montnegre_2</t>
+          <t xml:space="preserve">    Montnegre_1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  187 (8.42%)   </t>
+          <t xml:space="preserve">  223 (10.0%)   </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Marc_Aureli</t>
+          <t xml:space="preserve">    Montnegre_2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  331 (14.9%)   </t>
+          <t xml:space="preserve">  187 (8.42%)   </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1383,12 +1383,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Sant_Elies</t>
+          <t xml:space="preserve">    Marc_Aureli</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  388 (17.5%)   </t>
+          <t xml:space="preserve">  331 (14.9%)   </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Lluch</t>
+          <t xml:space="preserve">    Sant_Elies</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  340 (15.3%)   </t>
+          <t xml:space="preserve">  388 (17.5%)   </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1417,29 +1417,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Heart failure, N (%)</t>
+          <t xml:space="preserve">    Lluch</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  462 (20.8%)   </t>
+          <t xml:space="preserve">  340 (15.3%)   </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ischemic heart disease, N (%)</t>
+          <t>Heart failure, N (%)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  233 (10.5%)   </t>
+          <t xml:space="preserve">  462 (20.8%)   </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Arrhythmias, N (%)</t>
+          <t>Ischemic heart disease, N (%)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  625 (28.1%)   </t>
+          <t xml:space="preserve">  233 (10.5%)   </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dementia, N (%)</t>
+          <t>Arrhythmias, N (%)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  394 (17.7%)   </t>
+          <t xml:space="preserve">  625 (28.1%)   </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1485,12 +1485,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Parkinson, N (%)</t>
+          <t>Dementia, N (%)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  157 (7.07%)   </t>
+          <t xml:space="preserve">  394 (17.7%)   </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1502,12 +1502,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Stroke, N (%)</t>
+          <t>Parkinson, N (%)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">  352 (15.8%)   </t>
+          <t xml:space="preserve">  157 (7.07%)   </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Diabetes, N (%)</t>
+          <t>Stroke, N (%)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  450 (20.3%)   </t>
+          <t xml:space="preserve">  352 (15.8%)   </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1536,12 +1536,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hyperlipidemia, N (%)</t>
+          <t>Diabetes, N (%)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  271 (12.2%)   </t>
+          <t xml:space="preserve">  450 (20.3%)   </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Chronic Kidney Disease, N (%)</t>
+          <t>Hyperlipidemia, N (%)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  664 (29.9%)   </t>
+          <t xml:space="preserve">  271 (12.2%)   </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COPD, N (%)</t>
+          <t>Chronic Kidney Disease, N (%)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  351 (15.8%)   </t>
+          <t xml:space="preserve">  664 (29.9%)   </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Respiratory failure, N (%)</t>
+          <t>COPD, N (%)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (2.43%)   </t>
+          <t xml:space="preserve">  351 (15.8%)   </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1604,12 +1604,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Osteoarthritis, N (%)</t>
+          <t>Respiratory failure, N (%)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1057 (47.6%)  </t>
+          <t xml:space="preserve">   54 (2.43%)   </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hip fracture, N (%)</t>
+          <t>Arthritis or osteoarthritis, N (%)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">   21 (0.95%)   </t>
+          <t xml:space="preserve">  1057 (47.6%)  </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Osteoporosis, N (%)</t>
+          <t>Hip fracture, N (%)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">  517 (23.3%)   </t>
+          <t xml:space="preserve">   21 (0.95%)   </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Depression, N (%)</t>
+          <t>Osteoporosis, N (%)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">  555 (25.0%)   </t>
+          <t xml:space="preserve">  517 (23.3%)   </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1672,12 +1672,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Anxiety, N (%)</t>
+          <t>Anxiety or depression, N (%)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">  523 (23.5%)   </t>
+          <t xml:space="preserve">  891 (40.1%)   </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1740,12 +1740,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Chronic_heart_failure, N (%)</t>
+          <t>Cancer, N (%)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">  462 (20.8%)   </t>
+          <t xml:space="preserve">   99 (4.46%)   </t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1757,49 +1757,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cancer, N (%)</t>
+          <t>Liver_disease, N (%)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">   79 (3.56%)   </t>
+          <t xml:space="preserve">   9 (0.41%)    </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
-        <is>
-          <t>2221</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Metástasis, N (%)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   25 (1.13%)   </t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2221</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Liver_disease, N (%)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   9 (0.41%)    </t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
         <is>
           <t>2221</t>
         </is>
